--- a/numista_backend/NumisMate_Collection_Template.xlsx
+++ b/numista_backend/NumisMate_Collection_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ericd\Documents\MyVertexProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ericd\Documents\MyVertexProject\numista_backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="14" documentId="11_597D82F6F613C8264F2C4CC4BDFB5AF864F6FFB4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B48C534-3434-477A-B8D8-DE2AB760F2E7}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="4596" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
